--- a/output/pdf_financials_xlsx/IIP.UN.xlsx
+++ b/output/pdf_financials_xlsx/IIP.UN.xlsx
@@ -7506,25 +7506,25 @@
         </is>
       </c>
       <c r="C103" s="3" t="n">
-        <v>0</v>
+        <v>-274.069</v>
       </c>
       <c r="D103" s="3" t="n">
-        <v>0</v>
+        <v>-0.199596</v>
       </c>
       <c r="E103" s="3" t="n">
-        <v>0</v>
+        <v>0.000205</v>
       </c>
       <c r="F103" s="3" t="n">
-        <v>0</v>
+        <v>-0.000723</v>
       </c>
       <c r="G103" s="3" t="n">
-        <v>0</v>
+        <v>0.000204</v>
       </c>
       <c r="H103" s="3" t="n">
-        <v>0</v>
+        <v>0.000351</v>
       </c>
       <c r="I103" s="3" t="n">
-        <v>0</v>
+        <v>-0.000974</v>
       </c>
       <c r="J103" s="1" t="inlineStr">
         <is>
@@ -7710,25 +7710,25 @@
         </is>
       </c>
       <c r="C106" s="3" t="n">
-        <v>180.965</v>
+        <v>-93.104</v>
       </c>
       <c r="D106" s="3" t="n">
-        <v>1.241499</v>
+        <v>1.041903</v>
       </c>
       <c r="E106" s="3" t="n">
-        <v>0.004753</v>
+        <v>0.004958</v>
       </c>
       <c r="F106" s="3" t="n">
-        <v>-0.002529</v>
+        <v>-0.003252</v>
       </c>
       <c r="G106" s="3" t="n">
-        <v>0.003062</v>
+        <v>0.003266</v>
       </c>
       <c r="H106" s="3" t="n">
-        <v>0.007324</v>
+        <v>0.007675</v>
       </c>
       <c r="I106" s="3" t="n">
-        <v>0.005681</v>
+        <v>0.004707</v>
       </c>
       <c r="J106" s="1" t="inlineStr">
         <is>
@@ -10123,7 +10123,11 @@
           <t>Prepaids and deposits 10</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>PrepaidAssets</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
           <t>-</t>
@@ -11832,7 +11836,11 @@
           <t>Prepaids and deposits</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>PrepaidAssets</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr">
         <is>
           <t>-</t>
@@ -18455,7 +18463,11 @@
           <t>Prepaids and deposits 2,529</t>
         </is>
       </c>
-      <c r="D84" t="inlineStr"/>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>PrepaidAssets</t>
+        </is>
+      </c>
       <c r="E84" t="inlineStr">
         <is>
           <t>-</t>
@@ -35949,7 +35961,11 @@
           <t>Prepaids and deposits</t>
         </is>
       </c>
-      <c r="D248" t="inlineStr"/>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
       <c r="E248" t="inlineStr">
         <is>
           <t>-</t>
@@ -38323,7 +38339,11 @@
           <t>Distributions declared to Unitholders - - (10,316) (10,316) (10,316) Prepaids and deposits</t>
         </is>
       </c>
-      <c r="D270" t="inlineStr"/>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
       <c r="E270" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/IIP.UN.xlsx
+++ b/output/pdf_financials_xlsx/IIP.UN.xlsx
@@ -2803,58 +2803,58 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>221.231</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.011768</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>1.2e-05</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.024793</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.000435</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.001234</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.666</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.771</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.000491</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.000385</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.000523</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.000753</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.051642</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.002064</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.004267</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>0.002547</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>0</v>
+        <v>0.004524</v>
       </c>
       <c r="T34" s="3" t="n">
-        <v>0</v>
+        <v>0.003679</v>
       </c>
     </row>
     <row r="35">
@@ -2935,58 +2935,58 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>221.231</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.011768</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>1.2e-05</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.024793</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.000435</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.001234</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.666</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.771</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.000491</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.000385</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.000523</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.000753</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.051642</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>0.002064</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>0.004267</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0</v>
+        <v>0.002547</v>
       </c>
       <c r="S36" s="3" t="n">
-        <v>0</v>
+        <v>0.004524</v>
       </c>
       <c r="T36" s="3" t="n">
-        <v>0</v>
+        <v>0.003679</v>
       </c>
     </row>
     <row r="37">
@@ -10452,7 +10452,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -18691,7 +18691,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
